--- a/templates/samples/SALES_IMPORT_SIMULATION.xlsx
+++ b/templates/samples/SALES_IMPORT_SIMULATION.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="262">
   <si>
     <t>Date</t>
   </si>
@@ -207,6 +207,36 @@
     <t>A6 · suggest · expect: HELD, and a correction is offered → "iPhone 13"</t>
   </si>
   <si>
+    <t>AMAZON-A7</t>
+  </si>
+  <si>
+    <t>OP-A7-CODE</t>
+  </si>
+  <si>
+    <t>359900000000205</t>
+  </si>
+  <si>
+    <t>iPhone 16</t>
+  </si>
+  <si>
+    <t>A7 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
+    <t>AMAZON-A8</t>
+  </si>
+  <si>
+    <t>OP-A8-CODE</t>
+  </si>
+  <si>
+    <t>359900000000206</t>
+  </si>
+  <si>
+    <t>Galaxy A55</t>
+  </si>
+  <si>
+    <t>A8 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
     <t>Payment Mode</t>
   </si>
   <si>
@@ -264,6 +294,21 @@
     <t>B3 · suggest · expect: HELD, and a correction is offered → "NIHAL"</t>
   </si>
   <si>
+    <t>BM-B4</t>
+  </si>
+  <si>
+    <t>OP-B4-CODE</t>
+  </si>
+  <si>
+    <t>359900000000303</t>
+  </si>
+  <si>
+    <t>TOTALLY MADE UP LTD</t>
+  </si>
+  <si>
+    <t>B4 · held-supp · expect: HELD: supplier not on file, and no close match to offer</t>
+  </si>
+  <si>
     <t>BM-B5</t>
   </si>
   <si>
@@ -279,6 +324,45 @@
     <t>B5 · suggest · expect: HELD, and a correction is offered → "Galaxy S23 Ultra" → "NIHAL"</t>
   </si>
   <si>
+    <t>BM-B6</t>
+  </si>
+  <si>
+    <t>OP-B6-CODE</t>
+  </si>
+  <si>
+    <t>359900000000305</t>
+  </si>
+  <si>
+    <t>Pixel 8</t>
+  </si>
+  <si>
+    <t>B6 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
+    <t>BM-B7</t>
+  </si>
+  <si>
+    <t>OP-B7-CODE</t>
+  </si>
+  <si>
+    <t>GENERIC</t>
+  </si>
+  <si>
+    <t>B7 · blocked · expect: blocked by the pre-existing presence/format checks</t>
+  </si>
+  <si>
+    <t>BM-B8</t>
+  </si>
+  <si>
+    <t>OP-B8-CODE</t>
+  </si>
+  <si>
+    <t>359900000000306</t>
+  </si>
+  <si>
+    <t>B8 · blocked · expect: blocked by the pre-existing presence/format checks</t>
+  </si>
+  <si>
     <t>Units</t>
   </si>
   <si>
@@ -315,6 +399,21 @@
     <t>E1 · reconcile · expect: matched unit — flips to SOLD, no completion row</t>
   </si>
   <si>
+    <t>EBAY-E2</t>
+  </si>
+  <si>
+    <t>OP-E2-CODE</t>
+  </si>
+  <si>
+    <t>359900000000401</t>
+  </si>
+  <si>
+    <t>Pixel 7 Pro</t>
+  </si>
+  <si>
+    <t>E2 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
     <t>EBAY-E3</t>
   </si>
   <si>
@@ -408,6 +507,21 @@
     <t>E7 · suggest · expect: HELD, and a correction is offered → "MOBILE WHOLESALE LTD"</t>
   </si>
   <si>
+    <t>EBAY-E8</t>
+  </si>
+  <si>
+    <t>OP-E8-CODE</t>
+  </si>
+  <si>
+    <t>359900000000404</t>
+  </si>
+  <si>
+    <t>Galaxy S22 Ultra</t>
+  </si>
+  <si>
+    <t>E8 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
     <t>VAT 20%</t>
   </si>
   <si>
@@ -456,6 +570,51 @@
     <t>O3 · suggest · expect: HELD, and a correction is offered → "iPhone 15 Pro Max"</t>
   </si>
   <si>
+    <t>ONBUY-O4</t>
+  </si>
+  <si>
+    <t>OP-O4-CODE</t>
+  </si>
+  <si>
+    <t>359900000000503</t>
+  </si>
+  <si>
+    <t>iPhone 15 Pro</t>
+  </si>
+  <si>
+    <t>O4 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
+    <t>ONBUY-O5</t>
+  </si>
+  <si>
+    <t>OP-O5-CODE</t>
+  </si>
+  <si>
+    <t>359900000000504</t>
+  </si>
+  <si>
+    <t>CELLHUB TRADING</t>
+  </si>
+  <si>
+    <t>O5 · held-supp · expect: HELD: supplier not on file, and no close match to offer</t>
+  </si>
+  <si>
+    <t>ONBUY-O6</t>
+  </si>
+  <si>
+    <t>OP-O6-CODE</t>
+  </si>
+  <si>
+    <t>359900000000505</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>O6 · blocked · expect: blocked by the pre-existing presence/format checks</t>
+  </si>
+  <si>
     <t>ONBUY-O7</t>
   </si>
   <si>
@@ -468,6 +627,21 @@
     <t>O7 · ready · expect: orphan with full audit data — creates a unit</t>
   </si>
   <si>
+    <t>ONBUY-O8</t>
+  </si>
+  <si>
+    <t>OP-O8-CODE</t>
+  </si>
+  <si>
+    <t>359900000000507</t>
+  </si>
+  <si>
+    <t>Galaxy A34</t>
+  </si>
+  <si>
+    <t>O8 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
     <t>Commission VAT</t>
   </si>
   <si>
@@ -525,6 +699,21 @@
     <t>T4 · suggest · expect: HELD, and a correction is offered → "iPhone 14"</t>
   </si>
   <si>
+    <t>TEMU-T5</t>
+  </si>
+  <si>
+    <t>OP-T5-CODE</t>
+  </si>
+  <si>
+    <t>359900000000603</t>
+  </si>
+  <si>
+    <t>Redmi Note 12</t>
+  </si>
+  <si>
+    <t>T5 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
     <t>TEMU-T6</t>
   </si>
   <si>
@@ -537,6 +726,21 @@
     <t>T6 · ready · expect: orphan with full audit data — creates a unit</t>
   </si>
   <si>
+    <t>TEMU-T7</t>
+  </si>
+  <si>
+    <t>OP-T7-CODE</t>
+  </si>
+  <si>
+    <t>359900000000605</t>
+  </si>
+  <si>
+    <t>Pixel 6a</t>
+  </si>
+  <si>
+    <t>T7 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
+  </si>
+  <si>
     <t>TEMU-T8</t>
   </si>
   <si>
@@ -550,9 +754,6 @@
   </si>
   <si>
     <t>SALES TEMPLATE — same columns as the Sales Report</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>What this is</t>
@@ -1000,74 +1201,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="B1" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>184</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>187</v>
+        <v>254</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -1384,6 +1585,76 @@
       </c>
       <c r="AE7" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>300</v>
+      </c>
+      <c r="K8">
+        <v>420</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>180</v>
+      </c>
+      <c r="K9">
+        <v>260</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -1426,7 +1697,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -1444,10 +1715,10 @@
         <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="Q1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
@@ -1494,16 +1765,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -1521,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -1529,19 +1800,19 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1556,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -1564,19 +1835,19 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1591,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -1599,34 +1870,174 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
         <v>84</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>170</v>
+      </c>
+      <c r="L5">
+        <v>250</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>380</v>
+      </c>
+      <c r="L6">
+        <v>520</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" t="s">
         <v>85</v>
       </c>
-      <c r="H5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>380</v>
-      </c>
-      <c r="L5">
-        <v>520</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>86</v>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>250</v>
+      </c>
+      <c r="L7">
+        <v>340</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>200</v>
+      </c>
+      <c r="L8">
+        <v>300</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>300</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1637,7 +2048,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -1666,7 +2077,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
@@ -1684,16 +2095,16 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="S1" t="s">
         <v>17</v>
@@ -1702,10 +2113,10 @@
         <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="V1" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="W1" t="s">
         <v>19</v>
@@ -1749,16 +2160,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -1776,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
@@ -1784,34 +2195,34 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="K3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="AH3" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -1819,43 +2230,34 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="K4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="AD4" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>109</v>
-      </c>
       <c r="AH4" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -1863,16 +2265,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
@@ -1881,25 +2283,25 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="K5">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="AE5" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AG5" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="AH5" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -1907,16 +2309,16 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
@@ -1925,25 +2327,25 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="K6">
-        <v>390</v>
+        <v>310</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="AE6" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="AG6" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AH6" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
@@ -1951,34 +2353,113 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
+        <v>265</v>
+      </c>
+      <c r="K7">
+        <v>390</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>154</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>210</v>
       </c>
-      <c r="K7">
+      <c r="K8">
         <v>300</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>129</v>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>330</v>
+      </c>
+      <c r="K9">
+        <v>450</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1989,7 +2470,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -2033,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="O1" t="s">
         <v>17</v>
@@ -2083,16 +2564,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2107,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="AB2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -2115,16 +2596,16 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="H3" t="s">
         <v>46</v>
@@ -2139,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -2147,16 +2628,16 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="H4" t="s">
         <v>46</v>
@@ -2171,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -2179,31 +2660,159 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I5">
+        <v>650</v>
+      </c>
+      <c r="J5">
+        <v>850</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I6">
+        <v>200</v>
+      </c>
+      <c r="J6">
+        <v>300</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7">
+        <v>200</v>
+      </c>
+      <c r="J7">
+        <v>300</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8">
         <v>380</v>
       </c>
-      <c r="J5">
+      <c r="J8">
         <v>520</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>149</v>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>150</v>
+      </c>
+      <c r="J9">
+        <v>220</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2214,7 +2823,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -2261,10 +2870,10 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="P1" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="Q1" t="s">
         <v>17</v>
@@ -2314,16 +2923,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="E2" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2341,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -2349,16 +2958,16 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s">
         <v>36</v>
@@ -2376,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -2384,13 +2993,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
         <v>41</v>
@@ -2411,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -2419,16 +3028,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="H5" t="s">
         <v>46</v>
@@ -2446,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>168</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -2454,34 +3063,34 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="K6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -2489,34 +3098,104 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="H7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>190</v>
+      </c>
+      <c r="K7">
+        <v>270</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>160</v>
+      </c>
+      <c r="K8">
+        <v>230</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" t="s">
         <v>46</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>170</v>
       </c>
-      <c r="K7">
+      <c r="K9">
         <v>250</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>176</v>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/templates/samples/SALES_IMPORT_SIMULATION.xlsx
+++ b/templates/samples/SALES_IMPORT_SIMULATION.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="266">
   <si>
     <t>Date</t>
   </si>
@@ -237,6 +237,21 @@
     <t>A8 · quiet · expect: HELD, and NO correction offered — near neighbour of a real model</t>
   </si>
   <si>
+    <t>AMAZON-A9</t>
+  </si>
+  <si>
+    <t>OP-A9-CODE</t>
+  </si>
+  <si>
+    <t>359900000000009</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>A9 · legacy · expect: matched unit whose stored model predates the catalogue — must NOT be held</t>
+  </si>
+  <si>
     <t>Payment Mode</t>
   </si>
   <si>
@@ -607,9 +622,6 @@
   </si>
   <si>
     <t>359900000000505</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>O6 · blocked · expect: blocked by the pre-existing presence/format checks</t>
@@ -1201,74 +1213,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B1" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -1279,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -1655,6 +1667,41 @@
       </c>
       <c r="AE9" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>260</v>
+      </c>
+      <c r="K10">
+        <v>380</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1697,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -1715,10 +1762,10 @@
         <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
@@ -1765,16 +1812,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -1792,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -1800,19 +1847,19 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1827,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -1835,19 +1882,19 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
         <v>89</v>
       </c>
-      <c r="E4" t="s">
-        <v>84</v>
-      </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1862,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -1870,19 +1917,19 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1897,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -1905,19 +1952,19 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1932,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -1940,19 +1987,19 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -1967,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -1975,19 +2022,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2002,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -2010,19 +2057,19 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2037,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2124,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
@@ -2095,16 +2142,16 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="P1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Q1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="R1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="S1" t="s">
         <v>17</v>
@@ -2113,10 +2160,10 @@
         <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="V1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="W1" t="s">
         <v>19</v>
@@ -2160,16 +2207,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2187,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
@@ -2195,19 +2242,19 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2222,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -2230,19 +2277,19 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -2257,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -2265,16 +2312,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
@@ -2292,16 +2339,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AE5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="AG5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AH5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -2309,13 +2356,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -2336,16 +2383,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AE6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AH6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
@@ -2353,13 +2400,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
         <v>41</v>
@@ -2380,16 +2427,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AE7" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG7" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AH7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
@@ -2397,19 +2444,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2424,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
@@ -2432,19 +2479,19 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2459,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2514,7 +2561,7 @@
         <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="O1" t="s">
         <v>17</v>
@@ -2564,16 +2611,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2588,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="AB2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -2596,16 +2643,16 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H3" t="s">
         <v>46</v>
@@ -2620,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -2628,16 +2675,16 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H4" t="s">
         <v>46</v>
@@ -2652,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -2660,16 +2707,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
         <v>46</v>
@@ -2684,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="AB5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -2692,19 +2739,19 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I6">
         <v>200</v>
@@ -2716,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -2724,19 +2771,19 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="I7">
         <v>200</v>
@@ -2748,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -2756,19 +2803,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>380</v>
@@ -2780,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
@@ -2788,19 +2835,19 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I9">
         <v>150</v>
@@ -2812,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2870,10 +2917,10 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q1" t="s">
         <v>17</v>
@@ -2923,16 +2970,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2950,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -2958,16 +3005,16 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
         <v>36</v>
@@ -2985,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -2993,13 +3040,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
         <v>41</v>
@@ -3020,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -3028,16 +3075,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H5" t="s">
         <v>46</v>
@@ -3055,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -3063,16 +3110,16 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H6" t="s">
         <v>46</v>
@@ -3090,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -3098,19 +3145,19 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3125,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3133,19 +3180,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D8" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -3160,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3168,16 +3215,16 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
         <v>46</v>
@@ -3195,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/templates/samples/SALES_IMPORT_SIMULATION.xlsx
+++ b/templates/samples/SALES_IMPORT_SIMULATION.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="271">
   <si>
     <t>Date</t>
   </si>
@@ -250,6 +250,21 @@
   </si>
   <si>
     <t>A9 · legacy · expect: matched unit whose stored model predates the catalogue — must NOT be held</t>
+  </si>
+  <si>
+    <t>AMAZON-A10</t>
+  </si>
+  <si>
+    <t>OP-A10-CODE</t>
+  </si>
+  <si>
+    <t>359900000000207</t>
+  </si>
+  <si>
+    <t>IPAD 11TG GEN</t>
+  </si>
+  <si>
+    <t>A10 · ready · expect: orphan with full audit data — creates a unit</t>
   </si>
   <si>
     <t>Payment Mode</t>
@@ -1213,7 +1228,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B1" t="s">
         <v>76</v>
@@ -1221,66 +1236,66 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1291,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -1702,6 +1717,41 @@
       </c>
       <c r="AE10" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>260</v>
+      </c>
+      <c r="K11">
+        <v>380</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1794,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -1762,10 +1812,10 @@
         <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
@@ -1812,16 +1862,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -1839,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -1847,19 +1897,19 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1874,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -1882,19 +1932,19 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
         <v>94</v>
       </c>
-      <c r="E4" t="s">
-        <v>89</v>
-      </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1909,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -1917,19 +1967,19 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1944,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -1952,19 +2002,19 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1979,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -1987,19 +2037,19 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2014,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -2022,19 +2072,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2049,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -2057,19 +2107,19 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2084,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2124,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
@@ -2142,16 +2192,16 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="P1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="Q1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="R1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="S1" t="s">
         <v>17</v>
@@ -2160,10 +2210,10 @@
         <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="V1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="W1" t="s">
         <v>19</v>
@@ -2207,16 +2257,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2234,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
@@ -2242,19 +2292,19 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2269,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -2277,19 +2327,19 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -2304,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -2312,16 +2362,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
@@ -2339,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AE5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AG5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AH5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
@@ -2356,13 +2406,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -2383,16 +2433,16 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AE6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AG6" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AH6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
@@ -2400,13 +2450,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
         <v>41</v>
@@ -2427,16 +2477,16 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AE7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AG7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AH7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
@@ -2444,19 +2494,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H8" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2471,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
@@ -2479,19 +2529,19 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2506,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2561,7 +2611,7 @@
         <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="O1" t="s">
         <v>17</v>
@@ -2611,16 +2661,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2635,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="AB2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
@@ -2643,16 +2693,16 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H3" t="s">
         <v>46</v>
@@ -2667,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -2675,16 +2725,16 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H4" t="s">
         <v>46</v>
@@ -2699,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -2707,16 +2757,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H5" t="s">
         <v>46</v>
@@ -2731,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="AB5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
@@ -2739,19 +2789,19 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I6">
         <v>200</v>
@@ -2763,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -2771,13 +2821,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -2795,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -2803,19 +2853,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I8">
         <v>380</v>
@@ -2827,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
@@ -2835,19 +2885,19 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I9">
         <v>150</v>
@@ -2859,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2917,10 +2967,10 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="P1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q1" t="s">
         <v>17</v>
@@ -2970,16 +3020,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -2997,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
@@ -3005,16 +3055,16 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s">
         <v>36</v>
@@ -3032,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -3040,13 +3090,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E4" t="s">
         <v>41</v>
@@ -3067,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -3075,16 +3125,16 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H5" t="s">
         <v>46</v>
@@ -3102,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -3110,16 +3160,16 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H6" t="s">
         <v>46</v>
@@ -3137,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -3145,19 +3195,19 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3172,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
@@ -3180,19 +3230,19 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -3207,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3215,16 +3265,16 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H9" t="s">
         <v>46</v>
@@ -3242,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/templates/samples/SALES_IMPORT_SIMULATION.xlsx
+++ b/templates/samples/SALES_IMPORT_SIMULATION.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="275">
   <si>
     <t>Date</t>
   </si>
@@ -91,6 +91,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -1228,74 +1240,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1306,10 +1318,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1403,25 +1415,37 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -1435,28 +1459,28 @@
       <c r="R2">
         <v>0</v>
       </c>
-      <c r="AE2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
         <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1470,28 +1494,28 @@
       <c r="R3">
         <v>0</v>
       </c>
-      <c r="AE3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1505,28 +1529,28 @@
       <c r="R4">
         <v>0</v>
       </c>
-      <c r="AE4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
         <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1540,28 +1564,28 @@
       <c r="R5">
         <v>0</v>
       </c>
-      <c r="AE5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1575,28 +1599,28 @@
       <c r="R6">
         <v>0</v>
       </c>
-      <c r="AE6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -1610,28 +1634,28 @@
       <c r="R7">
         <v>0</v>
       </c>
-      <c r="AE7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -1645,28 +1669,28 @@
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="AE8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -1680,28 +1704,28 @@
       <c r="R9">
         <v>0</v>
       </c>
-      <c r="AE9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1715,28 +1739,28 @@
       <c r="R10">
         <v>0</v>
       </c>
-      <c r="AE10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AI10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1750,8 +1774,8 @@
       <c r="R11">
         <v>0</v>
       </c>
-      <c r="AE11" t="s">
-        <v>82</v>
+      <c r="AI11" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1762,10 +1786,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1794,7 +1818,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -1812,10 +1836,10 @@
         <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="R1" t="s">
         <v>17</v>
@@ -1856,25 +1880,37 @@
       <c r="AD1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -1888,28 +1924,28 @@
       <c r="R2">
         <v>0</v>
       </c>
-      <c r="AD2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1923,28 +1959,28 @@
       <c r="R3">
         <v>0</v>
       </c>
-      <c r="AD3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
         <v>98</v>
       </c>
-      <c r="D4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" t="s">
-        <v>94</v>
-      </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1958,28 +1994,28 @@
       <c r="R4">
         <v>0</v>
       </c>
-      <c r="AD4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1993,28 +2029,28 @@
       <c r="R5">
         <v>0</v>
       </c>
-      <c r="AD5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -2028,28 +2064,28 @@
       <c r="R6">
         <v>0</v>
       </c>
-      <c r="AD6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2063,28 +2099,28 @@
       <c r="R7">
         <v>0</v>
       </c>
-      <c r="AD7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2098,28 +2134,28 @@
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="AD8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2133,8 +2169,8 @@
       <c r="R9">
         <v>0</v>
       </c>
-      <c r="AD9" t="s">
-        <v>124</v>
+      <c r="AH9" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2145,10 +2181,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2174,7 +2210,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
@@ -2192,16 +2228,16 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="R1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="S1" t="s">
         <v>17</v>
@@ -2210,10 +2246,10 @@
         <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="V1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="W1" t="s">
         <v>19</v>
@@ -2251,25 +2287,37 @@
       <c r="AH1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2283,28 +2331,28 @@
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="AH2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AL2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2318,28 +2366,28 @@
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="AH3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AL3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -2353,28 +2401,28 @@
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="AH4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AL4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2388,37 +2436,37 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="AD5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>152</v>
-      </c>
       <c r="AH5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -2432,37 +2480,37 @@
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="AD6" t="s">
-        <v>157</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>158</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>159</v>
-      </c>
       <c r="AH6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2476,37 +2524,37 @@
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="AD7" t="s">
-        <v>164</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>165</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>166</v>
-      </c>
       <c r="AH7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>170</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2520,28 +2568,28 @@
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="AH8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AL8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2555,8 +2603,8 @@
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="AH9" t="s">
-        <v>177</v>
+      <c r="AL9" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2567,10 +2615,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2611,7 +2659,7 @@
         <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O1" t="s">
         <v>17</v>
@@ -2655,25 +2703,37 @@
       <c r="AB1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>470</v>
@@ -2684,28 +2744,28 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="AB2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I3">
         <v>700</v>
@@ -2716,28 +2776,28 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="AB3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>700</v>
@@ -2748,28 +2808,28 @@
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="AB4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I5">
         <v>650</v>
@@ -2780,28 +2840,28 @@
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="AB5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D6" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I6">
         <v>200</v>
@@ -2812,28 +2872,28 @@
       <c r="O6">
         <v>0</v>
       </c>
-      <c r="AB6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I7">
         <v>200</v>
@@ -2844,28 +2904,28 @@
       <c r="O7">
         <v>0</v>
       </c>
-      <c r="AB7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D8" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I8">
         <v>380</v>
@@ -2876,28 +2936,28 @@
       <c r="O8">
         <v>0</v>
       </c>
-      <c r="AB8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AF8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I9">
         <v>150</v>
@@ -2908,8 +2968,8 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="AB9" t="s">
-        <v>216</v>
+      <c r="AF9" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2920,10 +2980,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2967,10 +3027,10 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="P1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q1" t="s">
         <v>17</v>
@@ -3014,25 +3074,37 @@
       <c r="AD1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -3046,28 +3118,28 @@
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="AD2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -3081,28 +3153,28 @@
       <c r="Q3">
         <v>0</v>
       </c>
-      <c r="AD3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -3116,28 +3188,28 @@
       <c r="Q4">
         <v>0</v>
       </c>
-      <c r="AD4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3151,28 +3223,28 @@
       <c r="Q5">
         <v>0</v>
       </c>
-      <c r="AD5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -3186,28 +3258,28 @@
       <c r="Q6">
         <v>0</v>
       </c>
-      <c r="AD6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3221,28 +3293,28 @@
       <c r="Q7">
         <v>0</v>
       </c>
-      <c r="AD7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -3256,28 +3328,28 @@
       <c r="Q8">
         <v>0</v>
       </c>
-      <c r="AD8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AH8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -3291,8 +3363,8 @@
       <c r="Q9">
         <v>0</v>
       </c>
-      <c r="AD9" t="s">
-        <v>253</v>
+      <c r="AH9" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
